--- a/output/pdf_financials_xlsx/PAAS.xlsx
+++ b/output/pdf_financials_xlsx/PAAS.xlsx
@@ -6633,37 +6633,37 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>-0.232</v>
+        <v>25.77</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>1.618</v>
+        <v>91.468</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>1.618</v>
+        <v>91.468</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>2.146</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>0.964</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-0.137</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.485</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>-0.458</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>0.434</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>1.605</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>0.208</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>0</v>
@@ -6672,16 +6672,16 @@
         <v>0</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>-30.3</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>-31</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>0</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="92">
@@ -6726,10 +6726,10 @@
         <v>0</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>22.573</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>94.274</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>0</v>
@@ -12988,7 +12988,11 @@
           <t>Investment revaluation reserve</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -16000,7 +16004,11 @@
           <t>Investment revaluation reserve</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -22438,7 +22446,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -22542,7 +22554,11 @@
           <t>Investment revaluation reserve</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PAAS.xlsx
+++ b/output/pdf_financials_xlsx/PAAS.xlsx
@@ -2988,13 +2988,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>26.789</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>100.474</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>100.474</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>262.901</v>
@@ -3114,13 +3114,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>3.35</v>
+        <v>30.139</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>92.623</v>
+        <v>193.097</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>92.623</v>
+        <v>193.097</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>491.222</v>
@@ -3870,13 +3870,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>60.776</v>
+        <v>33.987</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>120.327</v>
+        <v>19.853</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>120.327</v>
+        <v>19.853</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>11.885</v>
@@ -46742,7 +46742,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -50222,7 +50222,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
